--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245843</v>
+        <v>122245845</v>
       </c>
       <c r="B2" t="n">
-        <v>90772</v>
+        <v>90761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R2" t="n">
-        <v>7112764</v>
+        <v>7112806</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245841</v>
+        <v>122245849</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770028</v>
+        <v>770253</v>
       </c>
       <c r="R3" t="n">
-        <v>7112618</v>
+        <v>7112770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245851</v>
+        <v>122245847</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>90761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770245</v>
+        <v>770260</v>
       </c>
       <c r="R4" t="n">
-        <v>7112757</v>
+        <v>7112762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245844</v>
+        <v>122245841</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>90726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770154</v>
+        <v>770028</v>
       </c>
       <c r="R5" t="n">
-        <v>7112686</v>
+        <v>7112618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245849</v>
+        <v>122245844</v>
       </c>
       <c r="B6" t="n">
-        <v>90768</v>
+        <v>92037</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770253</v>
+        <v>770154</v>
       </c>
       <c r="R6" t="n">
-        <v>7112770</v>
+        <v>7112686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245845</v>
+        <v>122245850</v>
       </c>
       <c r="B7" t="n">
-        <v>90754</v>
+        <v>90779</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770220</v>
+        <v>770225</v>
       </c>
       <c r="R7" t="n">
-        <v>7112806</v>
+        <v>7112798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245852</v>
+        <v>122245843</v>
       </c>
       <c r="B8" t="n">
-        <v>57522</v>
+        <v>90779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770220</v>
+        <v>770248</v>
       </c>
       <c r="R8" t="n">
-        <v>7112807</v>
+        <v>7112764</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245847</v>
+        <v>122245851</v>
       </c>
       <c r="B9" t="n">
-        <v>90754</v>
+        <v>90726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770260</v>
+        <v>770245</v>
       </c>
       <c r="R9" t="n">
-        <v>7112762</v>
+        <v>7112757</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245850</v>
+        <v>122245842</v>
       </c>
       <c r="B10" t="n">
-        <v>90772</v>
+        <v>90779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770225</v>
+        <v>770044</v>
       </c>
       <c r="R10" t="n">
-        <v>7112798</v>
+        <v>7112618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245842</v>
+        <v>122245852</v>
       </c>
       <c r="B11" t="n">
-        <v>90772</v>
+        <v>57525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770044</v>
+        <v>770220</v>
       </c>
       <c r="R11" t="n">
-        <v>7112618</v>
+        <v>7112807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245852</v>
+        <v>122245845</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>90779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         <v>770220</v>
       </c>
       <c r="R2" t="n">
-        <v>7112807</v>
+        <v>7112806</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245847</v>
+        <v>122245849</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>90793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770260</v>
+        <v>770253</v>
       </c>
       <c r="R3" t="n">
-        <v>7112762</v>
+        <v>7112770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245841</v>
+        <v>122245844</v>
       </c>
       <c r="B5" t="n">
-        <v>90744</v>
+        <v>92055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770028</v>
+        <v>770154</v>
       </c>
       <c r="R5" t="n">
-        <v>7112618</v>
+        <v>7112686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245851</v>
+        <v>122245852</v>
       </c>
       <c r="B6" t="n">
-        <v>90744</v>
+        <v>57527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770245</v>
+        <v>770220</v>
       </c>
       <c r="R6" t="n">
-        <v>7112757</v>
+        <v>7112807</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245843</v>
+        <v>122245841</v>
       </c>
       <c r="B7" t="n">
-        <v>90797</v>
+        <v>90744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770248</v>
+        <v>770028</v>
       </c>
       <c r="R7" t="n">
-        <v>7112764</v>
+        <v>7112618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245844</v>
+        <v>122245850</v>
       </c>
       <c r="B8" t="n">
-        <v>92055</v>
+        <v>90797</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770154</v>
+        <v>770225</v>
       </c>
       <c r="R8" t="n">
-        <v>7112686</v>
+        <v>7112798</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245850</v>
+        <v>122245843</v>
       </c>
       <c r="B9" t="n">
         <v>90797</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770225</v>
+        <v>770248</v>
       </c>
       <c r="R9" t="n">
-        <v>7112798</v>
+        <v>7112764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245845</v>
+        <v>122245847</v>
       </c>
       <c r="B10" t="n">
         <v>90779</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770220</v>
+        <v>770260</v>
       </c>
       <c r="R10" t="n">
-        <v>7112806</v>
+        <v>7112762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245849</v>
+        <v>122245851</v>
       </c>
       <c r="B11" t="n">
-        <v>90793</v>
+        <v>90744</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770253</v>
+        <v>770245</v>
       </c>
       <c r="R11" t="n">
-        <v>7112770</v>
+        <v>7112757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122245845</v>
       </c>
       <c r="B2" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245849</v>
+        <v>122245843</v>
       </c>
       <c r="B3" t="n">
-        <v>90793</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770253</v>
+        <v>770248</v>
       </c>
       <c r="R3" t="n">
-        <v>7112770</v>
+        <v>7112764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245842</v>
+        <v>122245852</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
+        <v>57527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770044</v>
+        <v>770220</v>
       </c>
       <c r="R4" t="n">
-        <v>7112618</v>
+        <v>7112807</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245844</v>
+        <v>122245849</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>90803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770154</v>
+        <v>770253</v>
       </c>
       <c r="R5" t="n">
-        <v>7112686</v>
+        <v>7112770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245852</v>
+        <v>122245841</v>
       </c>
       <c r="B6" t="n">
-        <v>57527</v>
+        <v>90754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770220</v>
+        <v>770028</v>
       </c>
       <c r="R6" t="n">
-        <v>7112807</v>
+        <v>7112618</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245841</v>
+        <v>122245847</v>
       </c>
       <c r="B7" t="n">
-        <v>90744</v>
+        <v>90789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770028</v>
+        <v>770260</v>
       </c>
       <c r="R7" t="n">
-        <v>7112618</v>
+        <v>7112762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245850</v>
+        <v>122245844</v>
       </c>
       <c r="B8" t="n">
-        <v>90797</v>
+        <v>92065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770225</v>
+        <v>770154</v>
       </c>
       <c r="R8" t="n">
-        <v>7112798</v>
+        <v>7112686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245843</v>
+        <v>122245842</v>
       </c>
       <c r="B9" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770248</v>
+        <v>770044</v>
       </c>
       <c r="R9" t="n">
-        <v>7112764</v>
+        <v>7112618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245847</v>
+        <v>122245850</v>
       </c>
       <c r="B10" t="n">
-        <v>90779</v>
+        <v>90807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770260</v>
+        <v>770225</v>
       </c>
       <c r="R10" t="n">
-        <v>7112762</v>
+        <v>7112798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>122245851</v>
       </c>
       <c r="B11" t="n">
-        <v>90744</v>
+        <v>90754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245845</v>
+        <v>122245841</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>90754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770220</v>
+        <v>770028</v>
       </c>
       <c r="R2" t="n">
-        <v>7112806</v>
+        <v>7112618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245843</v>
+        <v>122245845</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>90789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R3" t="n">
-        <v>7112764</v>
+        <v>7112806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245852</v>
+        <v>122245843</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>90807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770220</v>
+        <v>770248</v>
       </c>
       <c r="R4" t="n">
-        <v>7112807</v>
+        <v>7112764</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245849</v>
+        <v>122245844</v>
       </c>
       <c r="B5" t="n">
-        <v>90803</v>
+        <v>92065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770253</v>
+        <v>770154</v>
       </c>
       <c r="R5" t="n">
-        <v>7112770</v>
+        <v>7112686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245841</v>
+        <v>122245842</v>
       </c>
       <c r="B6" t="n">
-        <v>90754</v>
+        <v>90807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770028</v>
+        <v>770044</v>
       </c>
       <c r="R6" t="n">
         <v>7112618</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245844</v>
+        <v>122245849</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>90803</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770154</v>
+        <v>770253</v>
       </c>
       <c r="R8" t="n">
-        <v>7112686</v>
+        <v>7112770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245842</v>
+        <v>122245852</v>
       </c>
       <c r="B9" t="n">
-        <v>90807</v>
+        <v>57527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770044</v>
+        <v>770220</v>
       </c>
       <c r="R9" t="n">
-        <v>7112618</v>
+        <v>7112807</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245850</v>
+        <v>122245851</v>
       </c>
       <c r="B10" t="n">
-        <v>90807</v>
+        <v>90754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770225</v>
+        <v>770245</v>
       </c>
       <c r="R10" t="n">
-        <v>7112798</v>
+        <v>7112757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245851</v>
+        <v>122245850</v>
       </c>
       <c r="B11" t="n">
-        <v>90754</v>
+        <v>90807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770245</v>
+        <v>770225</v>
       </c>
       <c r="R11" t="n">
-        <v>7112757</v>
+        <v>7112798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245841</v>
+        <v>122245845</v>
       </c>
       <c r="B2" t="n">
-        <v>90754</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770028</v>
+        <v>770220</v>
       </c>
       <c r="R2" t="n">
-        <v>7112618</v>
+        <v>7112806</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245845</v>
+        <v>122245844</v>
       </c>
       <c r="B3" t="n">
-        <v>90789</v>
+        <v>92077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770220</v>
+        <v>770154</v>
       </c>
       <c r="R3" t="n">
-        <v>7112806</v>
+        <v>7112686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245843</v>
+        <v>122245850</v>
       </c>
       <c r="B4" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770248</v>
+        <v>770225</v>
       </c>
       <c r="R4" t="n">
-        <v>7112764</v>
+        <v>7112798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245844</v>
+        <v>122245851</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>90766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770154</v>
+        <v>770245</v>
       </c>
       <c r="R5" t="n">
-        <v>7112686</v>
+        <v>7112757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245842</v>
+        <v>122245843</v>
       </c>
       <c r="B6" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770044</v>
+        <v>770248</v>
       </c>
       <c r="R6" t="n">
-        <v>7112618</v>
+        <v>7112764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245847</v>
+        <v>122245852</v>
       </c>
       <c r="B7" t="n">
-        <v>90789</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770260</v>
+        <v>770220</v>
       </c>
       <c r="R7" t="n">
-        <v>7112762</v>
+        <v>7112807</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245849</v>
+        <v>122245847</v>
       </c>
       <c r="B8" t="n">
-        <v>90803</v>
+        <v>90801</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770253</v>
+        <v>770260</v>
       </c>
       <c r="R8" t="n">
-        <v>7112770</v>
+        <v>7112762</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245852</v>
+        <v>122245849</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>90815</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770220</v>
+        <v>770253</v>
       </c>
       <c r="R9" t="n">
-        <v>7112807</v>
+        <v>7112770</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245851</v>
+        <v>122245842</v>
       </c>
       <c r="B10" t="n">
-        <v>90754</v>
+        <v>90819</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770245</v>
+        <v>770044</v>
       </c>
       <c r="R10" t="n">
-        <v>7112757</v>
+        <v>7112618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245850</v>
+        <v>122245841</v>
       </c>
       <c r="B11" t="n">
-        <v>90807</v>
+        <v>90766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770225</v>
+        <v>770028</v>
       </c>
       <c r="R11" t="n">
-        <v>7112798</v>
+        <v>7112618</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245845</v>
+        <v>122245850</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770220</v>
+        <v>770225</v>
       </c>
       <c r="R2" t="n">
-        <v>7112806</v>
+        <v>7112798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245844</v>
+        <v>122245847</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>90808</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770154</v>
+        <v>770260</v>
       </c>
       <c r="R3" t="n">
-        <v>7112686</v>
+        <v>7112762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245850</v>
+        <v>122245851</v>
       </c>
       <c r="B4" t="n">
-        <v>90819</v>
+        <v>90773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770225</v>
+        <v>770245</v>
       </c>
       <c r="R4" t="n">
-        <v>7112798</v>
+        <v>7112757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245851</v>
+        <v>122245852</v>
       </c>
       <c r="B5" t="n">
-        <v>90766</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770245</v>
+        <v>770220</v>
       </c>
       <c r="R5" t="n">
-        <v>7112757</v>
+        <v>7112807</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245843</v>
+        <v>122245845</v>
       </c>
       <c r="B6" t="n">
-        <v>90819</v>
+        <v>90808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R6" t="n">
-        <v>7112764</v>
+        <v>7112806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245852</v>
+        <v>122245849</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>90822</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770220</v>
+        <v>770253</v>
       </c>
       <c r="R7" t="n">
-        <v>7112807</v>
+        <v>7112770</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245847</v>
+        <v>122245843</v>
       </c>
       <c r="B8" t="n">
-        <v>90801</v>
+        <v>90826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770260</v>
+        <v>770248</v>
       </c>
       <c r="R8" t="n">
-        <v>7112762</v>
+        <v>7112764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245849</v>
+        <v>122245842</v>
       </c>
       <c r="B9" t="n">
-        <v>90815</v>
+        <v>90826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770253</v>
+        <v>770044</v>
       </c>
       <c r="R9" t="n">
-        <v>7112770</v>
+        <v>7112618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245842</v>
+        <v>122245844</v>
       </c>
       <c r="B10" t="n">
-        <v>90819</v>
+        <v>92082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770044</v>
+        <v>770154</v>
       </c>
       <c r="R10" t="n">
-        <v>7112618</v>
+        <v>7112686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>122245841</v>
       </c>
       <c r="B11" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245850</v>
+        <v>122245847</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
+        <v>90808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770225</v>
+        <v>770260</v>
       </c>
       <c r="R2" t="n">
-        <v>7112798</v>
+        <v>7112762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245847</v>
+        <v>122245850</v>
       </c>
       <c r="B3" t="n">
-        <v>90808</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770260</v>
+        <v>770225</v>
       </c>
       <c r="R3" t="n">
-        <v>7112762</v>
+        <v>7112798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245849</v>
+        <v>122245843</v>
       </c>
       <c r="B7" t="n">
-        <v>90822</v>
+        <v>90826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770253</v>
+        <v>770248</v>
       </c>
       <c r="R7" t="n">
-        <v>7112770</v>
+        <v>7112764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245843</v>
+        <v>122245849</v>
       </c>
       <c r="B8" t="n">
-        <v>90826</v>
+        <v>90822</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770248</v>
+        <v>770253</v>
       </c>
       <c r="R8" t="n">
-        <v>7112764</v>
+        <v>7112770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245847</v>
+        <v>122245843</v>
       </c>
       <c r="B2" t="n">
-        <v>90808</v>
+        <v>90831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770260</v>
+        <v>770248</v>
       </c>
       <c r="R2" t="n">
-        <v>7112762</v>
+        <v>7112764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245850</v>
+        <v>122245844</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>92087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +788,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770225</v>
+        <v>770154</v>
       </c>
       <c r="R3" t="n">
-        <v>7112798</v>
+        <v>7112686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245851</v>
+        <v>122245842</v>
       </c>
       <c r="B4" t="n">
-        <v>90773</v>
+        <v>90831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +889,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770245</v>
+        <v>770044</v>
       </c>
       <c r="R4" t="n">
-        <v>7112757</v>
+        <v>7112618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,11 +996,6 @@
       <c r="E5" t="n">
         <v>103021</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -1102,7 +1082,7 @@
         <v>122245845</v>
       </c>
       <c r="B6" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,11 +1096,6 @@
       </c>
       <c r="E6" t="n">
         <v>1202</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1205,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245843</v>
+        <v>122245851</v>
       </c>
       <c r="B7" t="n">
-        <v>90826</v>
+        <v>90778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1192,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770248</v>
+        <v>770245</v>
       </c>
       <c r="R7" t="n">
-        <v>7112764</v>
+        <v>7112757</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245849</v>
+        <v>122245841</v>
       </c>
       <c r="B8" t="n">
-        <v>90822</v>
+        <v>90778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1293,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770253</v>
+        <v>770028</v>
       </c>
       <c r="R8" t="n">
-        <v>7112770</v>
+        <v>7112618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245842</v>
+        <v>122245849</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1398,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>1204</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770044</v>
+        <v>770253</v>
       </c>
       <c r="R9" t="n">
-        <v>7112618</v>
+        <v>7112770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245844</v>
+        <v>122245850</v>
       </c>
       <c r="B10" t="n">
-        <v>92082</v>
+        <v>90831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1495,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770154</v>
+        <v>770225</v>
       </c>
       <c r="R10" t="n">
-        <v>7112686</v>
+        <v>7112798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245841</v>
+        <v>122245847</v>
       </c>
       <c r="B11" t="n">
-        <v>90773</v>
+        <v>90813</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1596,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770028</v>
+        <v>770260</v>
       </c>
       <c r="R11" t="n">
-        <v>7112618</v>
+        <v>7112762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245843</v>
+        <v>122245844</v>
       </c>
       <c r="B2" t="n">
-        <v>90831</v>
+        <v>92100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>4364</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770248</v>
+        <v>770154</v>
       </c>
       <c r="R2" t="n">
-        <v>7112764</v>
+        <v>7112686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245844</v>
+        <v>122245842</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>90844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,20 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770154</v>
+        <v>770044</v>
       </c>
       <c r="R3" t="n">
-        <v>7112686</v>
+        <v>7112618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245842</v>
+        <v>122245851</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>90791</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,20 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770044</v>
+        <v>770245</v>
       </c>
       <c r="R4" t="n">
-        <v>7112618</v>
+        <v>7112757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245852</v>
+        <v>122245850</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>90844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,16 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770220</v>
+        <v>770225</v>
       </c>
       <c r="R5" t="n">
-        <v>7112807</v>
+        <v>7112798</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245845</v>
+        <v>122245843</v>
       </c>
       <c r="B6" t="n">
-        <v>90813</v>
+        <v>90844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,16 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770220</v>
+        <v>770248</v>
       </c>
       <c r="R6" t="n">
-        <v>7112806</v>
+        <v>7112764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245851</v>
+        <v>122245841</v>
       </c>
       <c r="B7" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,6 +1223,11 @@
       <c r="E7" t="n">
         <v>5447</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Fuscoporia viticola</t>
@@ -1215,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770245</v>
+        <v>770028</v>
       </c>
       <c r="R7" t="n">
-        <v>7112757</v>
+        <v>7112618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245841</v>
+        <v>122245847</v>
       </c>
       <c r="B8" t="n">
-        <v>90778</v>
+        <v>90826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1293,20 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770028</v>
+        <v>770260</v>
       </c>
       <c r="R8" t="n">
-        <v>7112618</v>
+        <v>7112762</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245849</v>
+        <v>122245845</v>
       </c>
       <c r="B9" t="n">
-        <v>90827</v>
+        <v>90826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,16 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770253</v>
+        <v>770220</v>
       </c>
       <c r="R9" t="n">
-        <v>7112770</v>
+        <v>7112806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245850</v>
+        <v>122245849</v>
       </c>
       <c r="B10" t="n">
-        <v>90831</v>
+        <v>90840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1499,16 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770225</v>
+        <v>770253</v>
       </c>
       <c r="R10" t="n">
-        <v>7112798</v>
+        <v>7112770</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245847</v>
+        <v>122245852</v>
       </c>
       <c r="B11" t="n">
-        <v>90813</v>
+        <v>57536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1600,16 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770260</v>
+        <v>770220</v>
       </c>
       <c r="R11" t="n">
-        <v>7112762</v>
+        <v>7112807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245844</v>
+        <v>122245842</v>
       </c>
       <c r="B2" t="n">
-        <v>92100</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770154</v>
+        <v>770044</v>
       </c>
       <c r="R2" t="n">
-        <v>7112686</v>
+        <v>7112618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245842</v>
+        <v>122245852</v>
       </c>
       <c r="B3" t="n">
-        <v>90844</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770044</v>
+        <v>770220</v>
       </c>
       <c r="R3" t="n">
-        <v>7112618</v>
+        <v>7112807</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245851</v>
+        <v>122245843</v>
       </c>
       <c r="B4" t="n">
-        <v>90791</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770245</v>
+        <v>770248</v>
       </c>
       <c r="R4" t="n">
-        <v>7112757</v>
+        <v>7112764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245850</v>
+        <v>122245849</v>
       </c>
       <c r="B5" t="n">
-        <v>90844</v>
+        <v>90853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770225</v>
+        <v>770253</v>
       </c>
       <c r="R5" t="n">
-        <v>7112798</v>
+        <v>7112770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245843</v>
+        <v>122245845</v>
       </c>
       <c r="B6" t="n">
-        <v>90844</v>
+        <v>90839</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R6" t="n">
-        <v>7112764</v>
+        <v>7112806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>122245841</v>
       </c>
       <c r="B7" t="n">
-        <v>90791</v>
+        <v>90804</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>122245847</v>
       </c>
       <c r="B8" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245845</v>
+        <v>122245844</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>92113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770220</v>
+        <v>770154</v>
       </c>
       <c r="R9" t="n">
-        <v>7112806</v>
+        <v>7112686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245849</v>
+        <v>122245850</v>
       </c>
       <c r="B10" t="n">
-        <v>90840</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770253</v>
+        <v>770225</v>
       </c>
       <c r="R10" t="n">
-        <v>7112770</v>
+        <v>7112798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245852</v>
+        <v>122245851</v>
       </c>
       <c r="B11" t="n">
-        <v>57536</v>
+        <v>90804</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770220</v>
+        <v>770245</v>
       </c>
       <c r="R11" t="n">
-        <v>7112807</v>
+        <v>7112757</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245852</v>
+        <v>122245843</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770220</v>
+        <v>770248</v>
       </c>
       <c r="R3" t="n">
-        <v>7112807</v>
+        <v>7112764</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245843</v>
+        <v>122245852</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R4" t="n">
-        <v>7112764</v>
+        <v>7112807</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245843</v>
+        <v>122245845</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770248</v>
+        <v>770220</v>
       </c>
       <c r="R3" t="n">
-        <v>7112764</v>
+        <v>7112806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245852</v>
+        <v>122245841</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>90804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770220</v>
+        <v>770028</v>
       </c>
       <c r="R4" t="n">
-        <v>7112807</v>
+        <v>7112618</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245849</v>
+        <v>122245852</v>
       </c>
       <c r="B5" t="n">
-        <v>90853</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770253</v>
+        <v>770220</v>
       </c>
       <c r="R5" t="n">
-        <v>7112770</v>
+        <v>7112807</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245845</v>
+        <v>122245851</v>
       </c>
       <c r="B6" t="n">
-        <v>90839</v>
+        <v>90804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770220</v>
+        <v>770245</v>
       </c>
       <c r="R6" t="n">
-        <v>7112806</v>
+        <v>7112757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245841</v>
+        <v>122245850</v>
       </c>
       <c r="B7" t="n">
-        <v>90804</v>
+        <v>90857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770028</v>
+        <v>770225</v>
       </c>
       <c r="R7" t="n">
-        <v>7112618</v>
+        <v>7112798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245847</v>
+        <v>122245844</v>
       </c>
       <c r="B8" t="n">
-        <v>90839</v>
+        <v>92113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770260</v>
+        <v>770154</v>
       </c>
       <c r="R8" t="n">
-        <v>7112762</v>
+        <v>7112686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245844</v>
+        <v>122245847</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>90839</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770154</v>
+        <v>770260</v>
       </c>
       <c r="R9" t="n">
-        <v>7112686</v>
+        <v>7112762</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245850</v>
+        <v>122245843</v>
       </c>
       <c r="B10" t="n">
         <v>90857</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770225</v>
+        <v>770248</v>
       </c>
       <c r="R10" t="n">
-        <v>7112798</v>
+        <v>7112764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245851</v>
+        <v>122245849</v>
       </c>
       <c r="B11" t="n">
-        <v>90804</v>
+        <v>90853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770245</v>
+        <v>770253</v>
       </c>
       <c r="R11" t="n">
-        <v>7112757</v>
+        <v>7112770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245843</v>
+        <v>122245849</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>90853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770248</v>
+        <v>770253</v>
       </c>
       <c r="R10" t="n">
-        <v>7112764</v>
+        <v>7112770</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245849</v>
+        <v>122245843</v>
       </c>
       <c r="B11" t="n">
-        <v>90853</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770253</v>
+        <v>770248</v>
       </c>
       <c r="R11" t="n">
-        <v>7112770</v>
+        <v>7112764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245842</v>
+        <v>122245849</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>90847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770044</v>
+        <v>770253</v>
       </c>
       <c r="R2" t="n">
-        <v>7112618</v>
+        <v>7112770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245845</v>
+        <v>122245847</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770220</v>
+        <v>770260</v>
       </c>
       <c r="R3" t="n">
-        <v>7112806</v>
+        <v>7112762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245841</v>
+        <v>122245851</v>
       </c>
       <c r="B4" t="n">
-        <v>90804</v>
+        <v>90798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770028</v>
+        <v>770245</v>
       </c>
       <c r="R4" t="n">
-        <v>7112618</v>
+        <v>7112757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245852</v>
+        <v>122245843</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>90851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770220</v>
+        <v>770248</v>
       </c>
       <c r="R5" t="n">
-        <v>7112807</v>
+        <v>7112764</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245851</v>
+        <v>122245844</v>
       </c>
       <c r="B6" t="n">
-        <v>90804</v>
+        <v>92114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770245</v>
+        <v>770154</v>
       </c>
       <c r="R6" t="n">
-        <v>7112757</v>
+        <v>7112686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245850</v>
+        <v>122245841</v>
       </c>
       <c r="B7" t="n">
-        <v>90857</v>
+        <v>90798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770225</v>
+        <v>770028</v>
       </c>
       <c r="R7" t="n">
-        <v>7112798</v>
+        <v>7112618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245844</v>
+        <v>122245852</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770154</v>
+        <v>770220</v>
       </c>
       <c r="R8" t="n">
-        <v>7112686</v>
+        <v>7112807</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245847</v>
+        <v>122245842</v>
       </c>
       <c r="B9" t="n">
-        <v>90839</v>
+        <v>90851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770260</v>
+        <v>770044</v>
       </c>
       <c r="R9" t="n">
-        <v>7112762</v>
+        <v>7112618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245849</v>
+        <v>122245845</v>
       </c>
       <c r="B10" t="n">
-        <v>90853</v>
+        <v>90833</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770253</v>
+        <v>770220</v>
       </c>
       <c r="R10" t="n">
-        <v>7112770</v>
+        <v>7112806</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245843</v>
+        <v>122245850</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770248</v>
+        <v>770225</v>
       </c>
       <c r="R11" t="n">
-        <v>7112764</v>
+        <v>7112798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40920-2024 artfynd.xlsx
+++ b/artfynd/A 40920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245849</v>
+        <v>122245850</v>
       </c>
       <c r="B2" t="n">
-        <v>90847</v>
+        <v>90851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770253</v>
+        <v>770225</v>
       </c>
       <c r="R2" t="n">
-        <v>7112770</v>
+        <v>7112798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245847</v>
+        <v>122245844</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>92114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770260</v>
+        <v>770154</v>
       </c>
       <c r="R3" t="n">
-        <v>7112762</v>
+        <v>7112686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245851</v>
+        <v>122245852</v>
       </c>
       <c r="B4" t="n">
-        <v>90798</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770245</v>
+        <v>770220</v>
       </c>
       <c r="R4" t="n">
-        <v>7112757</v>
+        <v>7112807</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245843</v>
+        <v>122245847</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770248</v>
+        <v>770260</v>
       </c>
       <c r="R5" t="n">
-        <v>7112764</v>
+        <v>7112762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245844</v>
+        <v>122245843</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>90851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770154</v>
+        <v>770248</v>
       </c>
       <c r="R6" t="n">
-        <v>7112686</v>
+        <v>7112764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122245852</v>
+        <v>122245842</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>770220</v>
+        <v>770044</v>
       </c>
       <c r="R8" t="n">
-        <v>7112807</v>
+        <v>7112618</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122245842</v>
+        <v>122245851</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>90798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>770044</v>
+        <v>770245</v>
       </c>
       <c r="R9" t="n">
-        <v>7112618</v>
+        <v>7112757</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122245845</v>
+        <v>122245849</v>
       </c>
       <c r="B10" t="n">
-        <v>90833</v>
+        <v>90847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>770220</v>
+        <v>770253</v>
       </c>
       <c r="R10" t="n">
-        <v>7112806</v>
+        <v>7112770</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122245850</v>
+        <v>122245845</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>90833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>770225</v>
+        <v>770220</v>
       </c>
       <c r="R11" t="n">
-        <v>7112798</v>
+        <v>7112806</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
